--- a/output/pdf_financials_xlsx/EPG.xlsx
+++ b/output/pdf_financials_xlsx/EPG.xlsx
@@ -639,16 +639,16 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.001197</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.184579</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.270105</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.096494</v>
       </c>
     </row>
     <row r="13">
@@ -940,16 +940,16 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-7.555277</v>
+        <v>-7.556474</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-11.117568</v>
+        <v>-11.302147</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-4.722511</v>
+        <v>-4.992616</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-12.482599</v>
+        <v>-12.579093</v>
       </c>
     </row>
     <row r="28">
@@ -978,16 +978,16 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-7.555277</v>
+        <v>-7.556474</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-11.117568</v>
+        <v>-11.302147</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-4.722511</v>
+        <v>-4.992616</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-12.482599</v>
+        <v>-12.579093</v>
       </c>
     </row>
     <row r="30">
@@ -1077,16 +1077,16 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>10.069257</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>7.755486</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>5.307426</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>3.531157</v>
       </c>
     </row>
     <row r="35">
@@ -1115,16 +1115,16 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0.077775</v>
+        <v>10.147032</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0.047055</v>
+        <v>7.802541</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0.02411</v>
+        <v>5.331536</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>9.851744999999999</v>
+        <v>13.382902</v>
       </c>
     </row>
     <row r="37">
@@ -1343,16 +1343,16 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>10.118519</v>
+        <v>0.049262</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>7.907324</v>
+        <v>0.151838</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>5.380601</v>
+        <v>0.073175</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>3.597946</v>
+        <v>0.066789</v>
       </c>
     </row>
     <row r="49">
@@ -3130,7 +3130,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" s="5" t="n">
@@ -6168,7 +6168,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -6638,7 +6638,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E106" s="5" t="n">

--- a/output/pdf_financials_xlsx/EPG.xlsx
+++ b/output/pdf_financials_xlsx/EPG.xlsx
@@ -544,16 +544,16 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.443189</v>
+        <v>1.288459</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.468346</v>
+        <v>1.248083</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.443913</v>
+        <v>1.113384</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.581434</v>
+        <v>1.190607</v>
       </c>
     </row>
     <row r="8">
@@ -601,16 +601,16 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.443189</v>
+        <v>1.288459</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.468346</v>
+        <v>1.248083</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.443913</v>
+        <v>1.113384</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.581434</v>
+        <v>1.190607</v>
       </c>
     </row>
     <row r="11">
@@ -620,16 +620,16 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>-0.443189</v>
+        <v>-1.288459</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>-0.468346</v>
+        <v>-1.248083</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>-0.443913</v>
+        <v>-1.113384</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>-0.581434</v>
+        <v>-1.190607</v>
       </c>
     </row>
     <row r="12">
@@ -2626,7 +2626,7 @@
         <v>0</v>
       </c>
       <c r="D115" s="3" t="n">
-        <v>0</v>
+        <v>0.037235</v>
       </c>
       <c r="E115" s="3" t="n">
         <v>0</v>
@@ -5110,7 +5110,11 @@
           <t>Proceeds on sale of marketable securities</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr"/>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E61" t="inlineStr">
         <is>
           <t>-</t>
@@ -5766,7 +5770,11 @@
           <t>Management &amp; director fees 12</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr"/>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E80" s="5" t="n">
         <v>0.84527</v>
       </c>
